--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,12 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603624.3020151512</v>
+        <v>603624</v>
       </c>
       <c r="R3" t="n">
-        <v>6724160.280279492</v>
+        <v>6724160</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +864,9 @@
           <t>2000-05-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2000-05-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>92807337</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,428 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129523837</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58404</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>603715</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6724112</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan fågelinventeringar C240036</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129523493</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58444</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>603772</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6724263</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan fågelinventeringar C240036</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129523489</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57137</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>603649</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6724127</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan fågelinventeringar C240036</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129523492</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58265</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>603747</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6724197</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan fågelinventeringar C240036</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -907,45 +907,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129523837</v>
+        <v>129523493</v>
       </c>
       <c r="B4" t="n">
-        <v>58404</v>
+        <v>58444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603715</v>
+        <v>603772</v>
       </c>
       <c r="R4" t="n">
-        <v>6724112</v>
+        <v>6724263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,12 +977,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,7 +1002,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Sanna Pousar</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1008,50 +1013,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129523493</v>
+        <v>129523837</v>
       </c>
       <c r="B5" t="n">
-        <v>58444</v>
+        <v>58404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603772</v>
+        <v>603715</v>
       </c>
       <c r="R5" t="n">
-        <v>6724263</v>
+        <v>6724112</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sanna Pousar</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -907,50 +907,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129523493</v>
+        <v>129523837</v>
       </c>
       <c r="B4" t="n">
-        <v>58444</v>
+        <v>58407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603772</v>
+        <v>603715</v>
       </c>
       <c r="R4" t="n">
-        <v>6724263</v>
+        <v>6724112</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,12 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sanna Pousar</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1013,45 +1008,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129523837</v>
+        <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58404</v>
+        <v>58447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603715</v>
+        <v>603772</v>
       </c>
       <c r="R5" t="n">
-        <v>6724112</v>
+        <v>6724263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Sanna Pousar</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1117,7 +1117,7 @@
         <v>129523489</v>
       </c>
       <c r="B6" t="n">
-        <v>57137</v>
+        <v>57140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129523492</v>
       </c>
       <c r="B7" t="n">
-        <v>58265</v>
+        <v>58268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129523837</v>
       </c>
       <c r="B4" t="n">
-        <v>58407</v>
+        <v>58412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58447</v>
+        <v>58452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129523489</v>
       </c>
       <c r="B6" t="n">
-        <v>57140</v>
+        <v>57145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129523492</v>
       </c>
       <c r="B7" t="n">
-        <v>58268</v>
+        <v>58273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129523837</v>
       </c>
       <c r="B4" t="n">
-        <v>58412</v>
+        <v>58413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58452</v>
+        <v>58453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129523489</v>
       </c>
       <c r="B6" t="n">
-        <v>57145</v>
+        <v>57146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129523492</v>
       </c>
       <c r="B7" t="n">
-        <v>58273</v>
+        <v>58274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -907,45 +907,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129523837</v>
+        <v>129523493</v>
       </c>
       <c r="B4" t="n">
-        <v>58413</v>
+        <v>58453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603715</v>
+        <v>603772</v>
       </c>
       <c r="R4" t="n">
-        <v>6724112</v>
+        <v>6724263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,12 +977,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,7 +1002,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Sanna Pousar</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1008,50 +1013,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129523493</v>
+        <v>129523837</v>
       </c>
       <c r="B5" t="n">
-        <v>58453</v>
+        <v>58413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603772</v>
+        <v>603715</v>
       </c>
       <c r="R5" t="n">
-        <v>6724263</v>
+        <v>6724112</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sanna Pousar</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -907,50 +907,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129523493</v>
+        <v>129523837</v>
       </c>
       <c r="B4" t="n">
-        <v>58453</v>
+        <v>58413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603772</v>
+        <v>603715</v>
       </c>
       <c r="R4" t="n">
-        <v>6724263</v>
+        <v>6724112</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,12 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sanna Pousar</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1013,45 +1008,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129523837</v>
+        <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58413</v>
+        <v>58453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603715</v>
+        <v>603772</v>
       </c>
       <c r="R5" t="n">
-        <v>6724112</v>
+        <v>6724263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Sanna Pousar</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58605</v>
+        <v>58607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129523489</v>
       </c>
       <c r="B6" t="n">
-        <v>57295</v>
+        <v>57297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58607</v>
+        <v>58608</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129523489</v>
       </c>
       <c r="B6" t="n">
-        <v>57297</v>
+        <v>57298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58608</v>
+        <v>58609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58609</v>
+        <v>58612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58612</v>
+        <v>58613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58613</v>
+        <v>58619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58619</v>
+        <v>58620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58620</v>
+        <v>58623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129523493</v>
       </c>
       <c r="B5" t="n">
-        <v>58623</v>
+        <v>58625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53644406</v>
+        <v>74250552</v>
       </c>
       <c r="B2" t="n">
-        <v>55392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208257</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Forsbackatippen, Gstr</t>
+          <t>Björkebäck 700 m NV, järnvägsspår till fd Forsbacka station, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603765.873877883</v>
+        <v>603301</v>
       </c>
       <c r="R2" t="n">
-        <v>6724092.703243745</v>
+        <v>6723634</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,24 +740,24 @@
           <t>Valbo</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>XG-Gäv-0571</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2008-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-05-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2008-07-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I tidig knopp, räknade ej antal, kontr.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,63 +766,73 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kulturmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Claes Lernmark</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Claes Lernmark</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92807337</v>
+        <v>93793835</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>107708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Forsbacka avfallstation O, mellan järnväg och väg, Gstr</t>
+          <t>Björkebäck 700 m NV, järnv t Forsb stn, skogskl.lok 116, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603624</v>
+        <v>603291</v>
       </c>
       <c r="R3" t="n">
-        <v>6724160</v>
+        <v>6723635</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-05-23</t>
+          <t>2013-07-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-05-23</t>
+          <t>2013-07-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,12 +878,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>skog, Granskog, med inslag av löv, frisk blåbärsskog, blockig sluttning</t>
+          <t>Kulturmark</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 202619N</t>
+          <t>Gst Fyndnr 313869H</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,27 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129523837</v>
+        <v>129523489</v>
       </c>
       <c r="B4" t="n">
-        <v>58413</v>
+        <v>57364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -936,16 +934,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603715</v>
+        <v>603649</v>
       </c>
       <c r="R4" t="n">
-        <v>6724112</v>
+        <v>6724127</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,12 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,7 +1000,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Sanna Pousar</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129523493</v>
+        <v>129523492</v>
       </c>
       <c r="B5" t="n">
-        <v>58625</v>
+        <v>58497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,39 +1022,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603772</v>
+        <v>603747</v>
       </c>
       <c r="R5" t="n">
-        <v>6724263</v>
+        <v>6724197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129523489</v>
+        <v>129523837</v>
       </c>
       <c r="B6" t="n">
-        <v>57298</v>
+        <v>58636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,16 +1131,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102954</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1143,21 +1149,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603649</v>
+        <v>603715</v>
       </c>
       <c r="R6" t="n">
-        <v>6724127</v>
+        <v>6724112</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,12 +1185,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,7 +1210,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sanna Pousar</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1220,53 +1221,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129523492</v>
+        <v>129523493</v>
       </c>
       <c r="B7" t="n">
-        <v>58274</v>
+        <v>58676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603747</v>
+        <v>603772</v>
       </c>
       <c r="R7" t="n">
-        <v>6724197</v>
+        <v>6724263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,6 +1322,562 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Bergslagsbanan fågelinventeringar C240036</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>53644406</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Forsbackatippen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>603766</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6724093</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-05-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-05-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Claes Lernmark</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Claes Lernmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97109221</v>
+      </c>
+      <c r="B9" t="n">
+        <v>108201</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Forsbacka 2 km N, Margretehill 800 m N, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>603340</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6723555</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2001-06-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2001-06-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kulturmark, grusigt järnvägsspår</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 230777N</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>92807337</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Forsbacka avfallstation O, mellan järnväg och väg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>603624</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6724160</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2000-05-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2000-05-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>skog, Granskog, med inslag av löv, frisk blåbärsskog, blockig sluttning</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 202619N</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>92807343</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Forsbacka avfallstation O, mellan järnväg och väg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>603568</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6724191</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2000-05-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2000-05-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>skog, Blandskog, blockig med blötsänkor. Växtplatsen var på trädsocklar i blöthålen</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 202614N</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>93814580</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björkebäck 700 m NV, järnvägsspår till fd Forsbacka station, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>603301</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6723634</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2005-07-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2005-07-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kulturmark, utmed järnvägsspår och väg</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 280705H</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 15365-2023 artfynd.xlsx
+++ b/artfynd/A 15365-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74250552</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93793835</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523489</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523492</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523837</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Bergslagsbanan fågelinventeringar C240036</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523493</t>
         </is>
       </c>
     </row>
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53644406</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97109221</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92807337</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1769,6 +1819,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92807343</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1880,8 +1935,26 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93814580</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>